--- a/data/programs.xlsx
+++ b/data/programs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\UbuntuOld\home\samnumbula\new_widget_ai_assistant_CDT_arch3_hybrid\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\local_bd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF9AB75-F73D-4381-8BA3-41AE208FEE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B8C498-3235-455A-8ADA-7463E958FE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="306">
   <si>
     <t>Направление</t>
   </si>
@@ -460,6 +460,9 @@
     <t>педагоги высшей квалификационной категории</t>
   </si>
   <si>
+    <t>https://forms.yandex.ru/u/6825cffaf47e7360e50f87d3/</t>
+  </si>
+  <si>
     <t>Шахматы</t>
   </si>
   <si>
@@ -467,9 +470,6 @@
   </si>
   <si>
     <t>4-6 лет</t>
-  </si>
-  <si>
-    <t>500 рублей / занятие</t>
   </si>
   <si>
     <r>
@@ -1017,12 +1017,6 @@
     <t xml:space="preserve">вторник, суббота 11.00 - 13.30  </t>
   </si>
   <si>
-    <t>https://forms.gle/KuLsrNxPaLtS5DH39</t>
-  </si>
-  <si>
-    <t>https://forms.gle/d73uxMDHNKCGBHvr7</t>
-  </si>
-  <si>
     <t>Ребенок получит базовые знания и навыки по школьным предметам: письмо, чтение, математика, окружающий мир, будет готов к учебному процессу и правилам поведения в школе.</t>
   </si>
   <si>
@@ -1039,6 +1033,90 @@
   </si>
   <si>
     <t>понедельник,  среда 18.10-18.50</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 93</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 92</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 91</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 90</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 89</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 88</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 87</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 86</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 85</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 84</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 83</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 82</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 81</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 80</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 79</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 78</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 77</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 76</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 75</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 74</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 73</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 72</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 71</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 70</t>
+  </si>
+  <si>
+    <t>по телефону: 8 995 834 09 69</t>
+  </si>
+  <si>
+    <t>550 рублей / занятие</t>
+  </si>
+  <si>
+    <t>https://forms.yandex.ru/u/6a43b4c56d2d73da05074937/</t>
+  </si>
+  <si>
+    <t>https://vk.com/away.php?to=https%3A%2F%2Fforms.yandex.ru%2Fu%2F6a43b4c56d2d73da05074937%2F&amp;utf=1</t>
   </si>
   <si>
     <t>Дизайн и моделирование одежды</t>
@@ -1054,7 +1132,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1132,8 +1210,7 @@
       <u/>
       <sz val="10"/>
       <color rgb="FF2F69C7"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="-apple-system"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1190,7 +1267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1316,10 +1393,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -1538,24 +1614,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z52"/>
-  <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="21" customWidth="1"/>
     <col min="2" max="2" width="20" style="21" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" style="21"/>
     <col min="4" max="4" width="16.42578125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="21" customWidth="1"/>
-    <col min="7" max="7" width="36" style="21" customWidth="1"/>
-    <col min="8" max="8" width="40" style="21" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" style="21" customWidth="1"/>
-    <col min="10" max="10" width="27.5703125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="19" style="21" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="48.28515625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="49.5703125" style="21" customWidth="1"/>
+    <col min="9" max="9" width="32" style="21" customWidth="1"/>
+    <col min="10" max="10" width="34.7109375" style="21" customWidth="1"/>
     <col min="11" max="11" width="29" style="21" customWidth="1"/>
     <col min="12" max="12" width="40.42578125" style="21" customWidth="1"/>
-    <col min="13" max="26" width="13.28515625" style="21"/>
+    <col min="13" max="13" width="58.85546875" style="21" customWidth="1"/>
+    <col min="14" max="26" width="13.28515625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="30">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -1593,9 +1670,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="120" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="114.75">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>11</v>
@@ -1625,15 +1702,18 @@
         <v>13</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>27</v>
+        <v>300</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" ht="120" x14ac:dyDescent="0.2">
+      <c r="M2" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="114.75">
       <c r="A3" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
@@ -1663,15 +1743,18 @@
         <v>15</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>27</v>
+        <v>299</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" ht="135" x14ac:dyDescent="0.2">
+      <c r="M3" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="105">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
@@ -1701,15 +1784,18 @@
         <v>19</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="165" x14ac:dyDescent="0.2">
+      <c r="M4" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="135">
       <c r="A5" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
@@ -1739,13 +1825,16 @@
         <v>22</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>26</v>
+        <v>297</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" ht="105" x14ac:dyDescent="0.2">
+      <c r="M5" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="90">
       <c r="A6" s="8" t="s">
         <v>132</v>
       </c>
@@ -1775,13 +1864,16 @@
         <v>31</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>36</v>
+        <v>296</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" ht="90" x14ac:dyDescent="0.2">
+      <c r="M6" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="76.5">
       <c r="A7" s="8" t="s">
         <v>132</v>
       </c>
@@ -1811,13 +1903,16 @@
         <v>34</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>35</v>
+        <v>295</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" s="25" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="M7" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" s="25" customFormat="1" ht="90">
       <c r="A8" s="32" t="s">
         <v>132</v>
       </c>
@@ -1846,13 +1941,15 @@
       <c r="J8" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="30" t="s">
-        <v>41</v>
+      <c r="K8" s="6" t="s">
+        <v>294</v>
       </c>
       <c r="L8" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="M8" s="34"/>
+      <c r="M8" s="30" t="s">
+        <v>41</v>
+      </c>
       <c r="N8" s="34"/>
       <c r="O8" s="34"/>
       <c r="P8" s="34"/>
@@ -1867,7 +1964,7 @@
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
-    <row r="9" spans="1:26" ht="165" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="120">
       <c r="A9" s="9" t="s">
         <v>42</v>
       </c>
@@ -1899,15 +1996,18 @@
         <v>206</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>45</v>
+        <v>293</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" s="25" customFormat="1" ht="150" x14ac:dyDescent="0.2">
+      <c r="M9" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" s="25" customFormat="1" ht="76.5">
       <c r="A10" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>47</v>
@@ -1932,13 +2032,15 @@
         <v>81</v>
       </c>
       <c r="J10" s="27"/>
-      <c r="K10" s="30" t="s">
-        <v>49</v>
+      <c r="K10" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="L10" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="M10" s="34"/>
+      <c r="M10" s="30" t="s">
+        <v>49</v>
+      </c>
       <c r="N10" s="34"/>
       <c r="O10" s="34"/>
       <c r="P10" s="34"/>
@@ -1953,9 +2055,9 @@
       <c r="Y10" s="34"/>
       <c r="Z10" s="34"/>
     </row>
-    <row r="11" spans="1:26" ht="150" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="76.5">
       <c r="A11" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>47</v>
@@ -1980,13 +2082,15 @@
         <v>81</v>
       </c>
       <c r="J11" s="27"/>
-      <c r="K11" s="30" t="s">
-        <v>49</v>
+      <c r="K11" s="6" t="s">
+        <v>291</v>
       </c>
       <c r="L11" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="M11" s="34"/>
+      <c r="M11" s="30" t="s">
+        <v>49</v>
+      </c>
       <c r="N11" s="34"/>
       <c r="O11" s="34"/>
       <c r="P11" s="34"/>
@@ -2001,9 +2105,9 @@
       <c r="Y11" s="34"/>
       <c r="Z11" s="34"/>
     </row>
-    <row r="12" spans="1:26" ht="150" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>139</v>
+    <row r="12" spans="1:26" ht="120">
+      <c r="A12" s="29" t="s">
+        <v>140</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>50</v>
@@ -2031,13 +2135,16 @@
         <v>54</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" s="25" customFormat="1" ht="120" x14ac:dyDescent="0.2">
+      <c r="M12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" s="25" customFormat="1" ht="105">
       <c r="A13" s="29" t="s">
         <v>79</v>
       </c>
@@ -2064,11 +2171,13 @@
         <v>81</v>
       </c>
       <c r="J13" s="27"/>
-      <c r="K13" s="30" t="s">
+      <c r="K13" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="L13" s="31"/>
+      <c r="M13" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="L13" s="31"/>
-      <c r="M13" s="34"/>
       <c r="N13" s="34"/>
       <c r="O13" s="34"/>
       <c r="P13" s="34"/>
@@ -2083,7 +2192,7 @@
       <c r="Y13" s="34"/>
       <c r="Z13" s="34"/>
     </row>
-    <row r="14" spans="1:26" ht="120" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="90">
       <c r="A14" s="8" t="s">
         <v>56</v>
       </c>
@@ -2115,13 +2224,16 @@
         <v>121</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>60</v>
+        <v>288</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" ht="105" x14ac:dyDescent="0.2">
+      <c r="M14" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="90">
       <c r="A15" s="8" t="s">
         <v>203</v>
       </c>
@@ -2153,15 +2265,18 @@
         <v>205</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>63</v>
+        <v>287</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" s="25" customFormat="1" ht="90" x14ac:dyDescent="0.2">
+      <c r="M15" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" s="25" customFormat="1" ht="75">
       <c r="A16" s="32" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>64</v>
@@ -2186,13 +2301,15 @@
       </c>
       <c r="I16" s="26"/>
       <c r="J16" s="27"/>
-      <c r="K16" s="30" t="s">
-        <v>67</v>
+      <c r="K16" s="6" t="s">
+        <v>286</v>
       </c>
       <c r="L16" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="M16" s="34"/>
+      <c r="M16" s="30" t="s">
+        <v>67</v>
+      </c>
       <c r="N16" s="34"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
@@ -2207,7 +2324,7 @@
       <c r="Y16" s="34"/>
       <c r="Z16" s="34"/>
     </row>
-    <row r="17" spans="1:26" ht="390" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="285">
       <c r="A17" s="8" t="s">
         <v>133</v>
       </c>
@@ -2217,7 +2334,7 @@
       <c r="C17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="26" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -2239,13 +2356,16 @@
         <v>121</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>71</v>
+        <v>285</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" ht="210" x14ac:dyDescent="0.2">
+      <c r="M17" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="165">
       <c r="A18" s="8" t="s">
         <v>134</v>
       </c>
@@ -2277,13 +2397,16 @@
         <v>209</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>74</v>
+        <v>284</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" ht="180" x14ac:dyDescent="0.2">
+      <c r="M18" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="135">
       <c r="A19" s="8" t="s">
         <v>75</v>
       </c>
@@ -2315,13 +2438,16 @@
         <v>210</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" ht="90" x14ac:dyDescent="0.2">
+      <c r="M19" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="89.25">
       <c r="A20" s="8" t="s">
         <v>99</v>
       </c>
@@ -2351,13 +2477,16 @@
         <v>220</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" ht="90" x14ac:dyDescent="0.2">
+      <c r="M20" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="89.25">
       <c r="A21" s="8" t="s">
         <v>99</v>
       </c>
@@ -2387,12 +2516,14 @@
         <v>219</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="M21"/>
+      <c r="M21" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="N21"/>
       <c r="O21"/>
       <c r="P21"/>
@@ -2407,7 +2538,7 @@
       <c r="Y21"/>
       <c r="Z21"/>
     </row>
-    <row r="22" spans="1:26" s="25" customFormat="1" ht="239.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" s="25" customFormat="1" ht="239.25" customHeight="1">
       <c r="A22" s="32" t="s">
         <v>85</v>
       </c>
@@ -2438,13 +2569,15 @@
       <c r="J22" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="K22" s="30" t="s">
-        <v>241</v>
+      <c r="K22" s="6" t="s">
+        <v>280</v>
       </c>
       <c r="L22" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="M22" s="34"/>
+      <c r="M22" s="30" t="s">
+        <v>241</v>
+      </c>
       <c r="N22" s="34"/>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
@@ -2459,7 +2592,7 @@
       <c r="Y22" s="34"/>
       <c r="Z22" s="34"/>
     </row>
-    <row r="23" spans="1:26" s="25" customFormat="1" ht="150" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" s="25" customFormat="1" ht="120">
       <c r="A23" s="32" t="s">
         <v>85</v>
       </c>
@@ -2490,13 +2623,15 @@
       <c r="J23" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="K23" s="30" t="s">
-        <v>240</v>
+      <c r="K23" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="L23" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="M23" s="34"/>
+      <c r="M23" s="30" t="s">
+        <v>240</v>
+      </c>
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
@@ -2511,7 +2646,7 @@
       <c r="Y23" s="34"/>
       <c r="Z23" s="34"/>
     </row>
-    <row r="24" spans="1:26" ht="210" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26" ht="165">
       <c r="A24" s="8" t="s">
         <v>85</v>
       </c>
@@ -2543,13 +2678,16 @@
         <v>206</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" ht="165" x14ac:dyDescent="0.2">
+      <c r="M24" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="120">
       <c r="A25" s="8" t="s">
         <v>85</v>
       </c>
@@ -2581,12 +2719,14 @@
         <v>221</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>94</v>
+        <v>277</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="M25" s="2"/>
+      <c r="M25" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="35"/>
@@ -2594,7 +2734,7 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="240" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26" ht="165">
       <c r="A26" s="11" t="s">
         <v>95</v>
       </c>
@@ -2626,13 +2766,16 @@
         <v>222</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>98</v>
+        <v>276</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" ht="102" x14ac:dyDescent="0.2">
+      <c r="M26" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="76.5">
       <c r="A27" s="11" t="s">
         <v>235</v>
       </c>
@@ -2668,7 +2811,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="191.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" ht="153">
       <c r="A28" s="11" t="s">
         <v>135</v>
       </c>
@@ -2694,13 +2837,13 @@
         <v>143</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>138</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>270</v>
+        <v>139</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>252</v>
@@ -2713,7 +2856,7 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="180" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="135">
       <c r="A29" s="9" t="s">
         <v>247</v>
       </c>
@@ -2734,7 +2877,7 @@
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>255</v>
@@ -2743,7 +2886,7 @@
         <v>138</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>270</v>
+        <v>139</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>253</v>
@@ -2756,12 +2899,12 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="195" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" ht="153">
       <c r="A30" s="9" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>248</v>
@@ -2788,7 +2931,7 @@
         <v>138</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>270</v>
+        <v>139</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>254</v>
@@ -2801,7 +2944,7 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
     </row>
-    <row r="31" spans="1:26" ht="90" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="75">
       <c r="A31" s="9" t="s">
         <v>249</v>
       </c>
@@ -2822,7 +2965,7 @@
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I31" s="9" t="s">
         <v>250</v>
@@ -2831,7 +2974,7 @@
         <v>46</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>270</v>
+        <v>139</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>251</v>
@@ -2844,21 +2987,21 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
     </row>
-    <row r="32" spans="1:26" ht="105" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" ht="90">
       <c r="A32" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>142</v>
+        <v>301</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>24</v>
@@ -2876,27 +3019,27 @@
         <v>144</v>
       </c>
       <c r="K32" s="43" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" ht="60">
       <c r="A33" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>145</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="D33" s="9" t="s">
+        <v>301</v>
+      </c>
       <c r="E33" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>24</v>
@@ -2914,15 +3057,15 @@
         <v>155</v>
       </c>
       <c r="K33" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="90" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:26" ht="75">
       <c r="A34" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>151</v>
@@ -2930,8 +3073,8 @@
       <c r="C34" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>142</v>
+      <c r="D34" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>264</v>
@@ -2952,13 +3095,13 @@
         <v>166</v>
       </c>
       <c r="K34" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="180" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:26" ht="135">
       <c r="A35" s="11" t="s">
         <v>75</v>
       </c>
@@ -2966,10 +3109,10 @@
         <v>146</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="2" t="s">
         <v>142</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="E35" s="21" t="s">
         <v>266</v>
@@ -2990,24 +3133,24 @@
         <v>89</v>
       </c>
       <c r="K35" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="240" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" ht="195">
       <c r="A36" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>147</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D36" s="2" t="s">
         <v>142</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="E36" s="21" t="s">
         <v>156</v>
@@ -3026,13 +3169,13 @@
         <v>48</v>
       </c>
       <c r="K36" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="105" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:26" ht="75">
       <c r="A37" s="11" t="s">
         <v>132</v>
       </c>
@@ -3040,13 +3183,13 @@
         <v>148</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D37" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="D37" s="9" t="s">
+        <v>301</v>
+      </c>
       <c r="E37" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>24</v>
@@ -3062,13 +3205,13 @@
         <v>31</v>
       </c>
       <c r="K37" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="225" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:26" ht="165">
       <c r="A38" s="11" t="s">
         <v>85</v>
       </c>
@@ -3076,10 +3219,10 @@
         <v>149</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D38" s="2" t="s">
         <v>142</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="E38" s="21" t="s">
         <v>157</v>
@@ -3100,13 +3243,13 @@
         <v>121</v>
       </c>
       <c r="K38" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="225" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:26" ht="165">
       <c r="A39" s="11" t="s">
         <v>85</v>
       </c>
@@ -3114,10 +3257,10 @@
         <v>149</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D39" s="2" t="s">
         <v>142</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>157</v>
@@ -3138,15 +3281,15 @@
         <v>165</v>
       </c>
       <c r="K39" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="90" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:26" ht="75">
       <c r="A40" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>150</v>
@@ -3154,8 +3297,8 @@
       <c r="C40" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>142</v>
+      <c r="D40" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>265</v>
@@ -3174,24 +3317,24 @@
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="22" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="240" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:26" ht="195">
       <c r="A41" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>147</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D41" s="2" t="s">
         <v>142</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="E41" s="21" t="s">
         <v>267</v>
@@ -3207,8 +3350,8 @@
         <v>81</v>
       </c>
       <c r="J41" s="18"/>
-      <c r="K41" s="44" t="s">
-        <v>271</v>
+      <c r="K41" s="22" t="s">
+        <v>302</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>258</v>
@@ -3228,101 +3371,99 @@
       <c r="Y41"/>
       <c r="Z41"/>
     </row>
-    <row r="42" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:26" ht="15">
       <c r="G42" s="12"/>
       <c r="H42" s="17"/>
       <c r="L42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" ht="15">
       <c r="G43" s="12"/>
       <c r="H43" s="14"/>
       <c r="L43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:26" ht="15">
       <c r="G44" s="12"/>
       <c r="H44" s="14"/>
       <c r="L44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" ht="15">
       <c r="G45" s="12"/>
       <c r="H45" s="23"/>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" ht="15">
       <c r="G46" s="12"/>
       <c r="L46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:26" ht="15">
       <c r="G47" s="12"/>
       <c r="H47" s="14"/>
       <c r="L47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:26" ht="15">
       <c r="G48" s="12"/>
       <c r="H48" s="24"/>
       <c r="L48" s="1"/>
     </row>
-    <row r="49" spans="7:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="7:12" ht="15">
       <c r="G49" s="12"/>
       <c r="H49" s="14"/>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="7:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="7:12" ht="15">
       <c r="G50" s="12"/>
       <c r="H50" s="14"/>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" spans="7:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="7:12" ht="15">
       <c r="G51" s="12"/>
       <c r="H51" s="24"/>
       <c r="L51" s="1"/>
     </row>
-    <row r="52" spans="7:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="7:12" ht="15">
       <c r="G52" s="12"/>
       <c r="H52" s="14"/>
       <c r="L52" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="K2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="K7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="K8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="K9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="K12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="K3" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="K14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="K16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="K17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="K18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K20" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="K24" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K25" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K26" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="K11" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K10" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="K23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K19" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K13" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K29" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K30" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K31" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="K33" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="K34" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="K35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="K36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="K37" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="K38" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="K39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="K40" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="K41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="M10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="M12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="M14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="M16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="M20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="M21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="M26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K32" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K34" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K35" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K36" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K37" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="K38" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K39" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="K40" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="K41" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K29" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="K30" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K31" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
